--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,18 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,12 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-512</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3790</v>
+        <v>4040</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4094</v>
+        <v>7505</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-304</v>
+        <v>-3465</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,27 +568,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-512</t>
+          <t>Nile Air NP-529</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3790</v>
+        <v>4082</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-7017</v>
+        <v>-3423</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +599,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,36 +613,36 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>Nile Air NP-629</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3846</v>
+        <v>4082</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-6961</v>
+        <v>-3423</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -676,36 +658,36 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Nile Air NP-627</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3846</v>
+        <v>4082</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-6961</v>
+        <v>-3423</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -721,36 +703,36 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Nile Air NP-427</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3846</v>
+        <v>4082</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-6961</v>
+        <v>-3423</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,27 +748,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-176</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3983</v>
+        <v>4082</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6824</v>
+        <v>-3423</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +779,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,27 +793,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3983</v>
+        <v>4082</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6824</v>
+        <v>-3423</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,9 +824,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,27 +838,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-327</t>
+          <t>Nile Air NP-427</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4011</v>
+        <v>4082</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-6796</v>
+        <v>-3423</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,9 +869,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,27 +883,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4011</v>
+        <v>4082</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-6796</v>
+        <v>-3423</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +914,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,36 +928,36 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-574</t>
+          <t>Nesma Airlines NE-510</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4673</v>
+        <v>6242</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-6134</v>
+        <v>-1263</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -991,36 +973,36 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-584</t>
+          <t>Nile Air NP-427</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4673</v>
+        <v>4082</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-6134</v>
+        <v>-3423</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1036,36 +1018,36 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-570</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4673</v>
+        <v>4082</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-6134</v>
+        <v>-3423</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1081,36 +1063,36 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-572</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4673</v>
+        <v>4082</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10807</v>
+        <v>7505</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-6134</v>
+        <v>-3423</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1126,36 +1108,36 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-590</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4673</v>
+        <v>5078</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10807</v>
+        <v>8207</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-6134</v>
+        <v>-3129</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1171,36 +1153,36 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-578</t>
+          <t>Nesma Airlines NE-176</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5086</v>
+        <v>5120</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10807</v>
+        <v>8207</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-5721</v>
+        <v>-3087</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1216,36 +1198,36 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-568</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5086</v>
+        <v>5120</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10807</v>
+        <v>8207</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-5721</v>
+        <v>-3087</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,40 +1243,40 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6437</v>
+        <v>5300</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10807</v>
+        <v>8207</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4370</v>
+        <v>-2907</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,36 +1288,36 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Air Arabia Egypt E5-363</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6740</v>
+        <v>5300</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10807</v>
+        <v>8207</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4067</v>
+        <v>-2907</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,36 +1333,36 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-667</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6740</v>
+        <v>7154</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10807</v>
+        <v>8207</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4067</v>
+        <v>-1053</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,27 +1378,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7623</v>
+        <v>7267</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>10807</v>
+        <v>8207</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-3184</v>
+        <v>-940</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,9 +1409,9 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,27 +1423,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-671</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7981</v>
+        <v>7267</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10807</v>
+        <v>8207</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2826</v>
+        <v>-940</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1486,7 +1468,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1478,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4772</v>
+        <v>7267</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>8533</v>
+        <v>8207</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-3761</v>
+        <v>-940</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1513,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1523,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-367</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4772</v>
+        <v>7379</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8533</v>
+        <v>8207</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-3761</v>
+        <v>-828</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1558,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1568,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-970</t>
+          <t>EgyptAir MS-661</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>5059</v>
+        <v>7575</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>8533</v>
+        <v>8207</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-3474</v>
+        <v>-632</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1603,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1613,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-176</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>5059</v>
+        <v>9287</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8533</v>
+        <v>8207</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-3474</v>
+        <v>1080</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1648,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>06-APR-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1658,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5059</v>
+        <v>6369</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>8533</v>
+        <v>6804</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-3474</v>
+        <v>-435</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1693,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>11-APR-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,26 +1703,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5059</v>
+        <v>7295</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>8533</v>
+        <v>6116</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-3474</v>
+        <v>1179</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1756,7 +1738,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,26 +1748,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-327</t>
+          <t>flynas XY-590</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>5155</v>
+        <v>4194</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>8533</v>
+        <v>11209</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-3378</v>
+        <v>-7015</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1801,7 +1783,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1793,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>flynas XY-578</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8091</v>
+        <v>4194</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>8533</v>
+        <v>11209</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-442</v>
+        <v>-7015</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
+        <v>20</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1828,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,26 +1838,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>flynas XY-566</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8091</v>
+        <v>4194</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>8533</v>
+        <v>11209</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-442</v>
+        <v>-7015</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
+        <v>20</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1873,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1883,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-325</t>
+          <t>flynas XY-568</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>8222</v>
+        <v>4194</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>8533</v>
+        <v>11209</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-311</v>
+        <v>-7015</v>
       </c>
       <c r="G32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
       <c r="I32" s="2" t="n">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1918,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1928,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7119</v>
+        <v>4475</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-4446</v>
+        <v>-6734</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1963,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1973,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-5112</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7126</v>
+        <v>4475</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-4439</v>
+        <v>-6734</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>25</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2008,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2018,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-970</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>7126</v>
+        <v>4615</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-4439</v>
+        <v>-6594</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2053,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,26 +2063,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-327</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7692</v>
+        <v>4615</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-3873</v>
+        <v>-6594</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2098,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,23 +2108,23 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>flynas XY-574</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>7967</v>
+        <v>6860</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-3598</v>
+        <v>-4349</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>0</v>
@@ -2161,7 +2143,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,23 +2153,23 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>flynas XY-584</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8381</v>
+        <v>6860</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-3184</v>
+        <v>-4349</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>0</v>
@@ -2206,7 +2188,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2198,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-510</t>
+          <t>flynas XY-570</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>8464</v>
+        <v>6860</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-3101</v>
+        <v>-4349</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2233,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>11-MAY-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2243,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>flynas XY-572</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>10201</v>
+        <v>6860</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1364</v>
+        <v>-4349</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2278,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>13-MAY-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2288,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>10201</v>
+        <v>4475</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1364</v>
+        <v>-6734</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2323,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>13-MAY-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2333,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>10669</v>
+        <v>4475</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-896</v>
+        <v>-6734</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2368,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>14-MAY-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2378,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-510</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>10214</v>
+        <v>4475</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1351</v>
+        <v>-6734</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2413,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>14-MAY-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2423,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>12902</v>
+        <v>4475</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11565</v>
+        <v>11209</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1337</v>
+        <v>-6734</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2476,36 +2458,36 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SM-457</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-510</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10214</v>
+        <v>4475</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10807</v>
+        <v>11209</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-593</v>
+        <v>-6734</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -2521,36 +2503,36 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>18-MAY-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SM-457</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>12902</v>
+        <v>4475</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>10807</v>
+        <v>11209</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>2095</v>
+        <v>-6734</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2548,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>18-MAY-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2558,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-510</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6161</v>
+        <v>4475</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>7140</v>
+        <v>11209</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-979</v>
+        <v>-6734</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2593,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,26 +2603,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-514</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>6740</v>
+        <v>4475</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>7140</v>
+        <v>11209</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-400</v>
+        <v>-6734</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2638,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,30 +2648,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-510</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5059</v>
+        <v>4475</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>7829</v>
+        <v>11209</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-2770</v>
+        <v>-6734</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>25</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2683,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2693,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>7623</v>
+        <v>5457</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>7829</v>
+        <v>11980</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-206</v>
+        <v>-6523</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2728,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,26 +2738,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>7168</v>
+        <v>5457</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>7829</v>
+        <v>11980</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-661</v>
+        <v>-6523</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2791,7 +2773,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,26 +2783,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>flyadeal F3-774</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5059</v>
+        <v>6288</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>8533</v>
+        <v>8908</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-3474</v>
+        <v>-2620</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2818,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2850,13 +2832,13 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>6286</v>
+        <v>9175</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>8533</v>
+        <v>9666</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-2247</v>
+        <v>-491</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2881,7 +2863,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2873,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>6286</v>
+        <v>9175</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>8533</v>
+        <v>9666</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-2247</v>
+        <v>-491</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2926,7 +2908,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2918,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>6396</v>
+        <v>9175</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>8533</v>
+        <v>9666</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-2137</v>
+        <v>-491</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>46</v>
@@ -2971,7 +2953,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2985,13 +2967,13 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>6699</v>
+        <v>9175</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>8533</v>
+        <v>9666</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1834</v>
+        <v>-491</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3008,231 +2990,6 @@
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>04-APR-26</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-671</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>7058</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>8533</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>-1475</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>04-APR-26</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-669</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>8533</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>-1365</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>04-APR-26</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>7623</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>8533</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>-910</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>11-APR-26</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>6782</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>5762</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>1020</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>30-APR-26</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-325</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>6571</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>5762</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>809</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -459,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -556,7 +556,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -533,26 +533,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10060</v>
+        <v>10102</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>14428</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4368</v>
+        <v>-4326</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10624</v>
+        <v>10215</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>14428</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3804</v>
+        <v>-4213</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -623,7 +623,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -668,26 +668,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12457</v>
+        <v>11004</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>14428</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1971</v>
+        <v>-3424</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,26 +803,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7280</v>
+        <v>12117</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11765</v>
+        <v>12540</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-4485</v>
+        <v>-423</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -848,26 +848,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11314</v>
+        <v>7280</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>11765</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-451</v>
+        <v>-4485</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9919</v>
+        <v>11314</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8059</v>
+        <v>11765</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1860</v>
+        <v>-451</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -920,186 +920,6 @@
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>08-JUL-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>9919</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>8059</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1860</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20-JUL-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>9919</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>8059</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>1860</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>9919</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>8750</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1169</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-410</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>13175</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>10990</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>2185</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -533,26 +533,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10102</v>
+        <v>10060</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>14428</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4326</v>
+        <v>-4368</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -578,17 +578,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10215</v>
+        <v>10102</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>14428</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4213</v>
+        <v>-4326</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -623,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11004</v>
+        <v>10215</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>14428</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3424</v>
+        <v>-4213</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -713,26 +713,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-645</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13315</v>
+        <v>11004</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>14428</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1113</v>
+        <v>-3424</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-659</t>
+          <t>EgyptAir MS-645</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -793,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-659</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12117</v>
+        <v>13315</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12540</v>
+        <v>14428</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-423</v>
+        <v>-1113</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -838,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,26 +848,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7280</v>
+        <v>12117</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11765</v>
+        <v>12540</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4485</v>
+        <v>-423</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -893,33 +893,303 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11314</v>
+        <v>7280</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>11765</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-451</v>
+        <v>-4485</v>
       </c>
       <c r="G10" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-332</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>13964</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>11765</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>2199</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>04-JUL-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>9919</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>8059</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1860</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>9919</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>8059</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1860</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>9919</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>8059</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1860</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>9919</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>8750</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>1169</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-410</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>13175</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>10990</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2185</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10060</v>
+        <v>9956</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14428</v>
+        <v>14280</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4368</v>
+        <v>-4324</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>20</v>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10102</v>
+        <v>9998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14428</v>
+        <v>14280</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4326</v>
+        <v>-4282</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10215</v>
+        <v>10110</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14428</v>
+        <v>14280</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4213</v>
+        <v>-4170</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11004</v>
+        <v>10891</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14428</v>
+        <v>14280</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3424</v>
+        <v>-3389</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11004</v>
+        <v>10891</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14428</v>
+        <v>14280</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3424</v>
+        <v>-3389</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>13315</v>
+        <v>13178</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14428</v>
+        <v>14280</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1113</v>
+        <v>-1102</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13315</v>
+        <v>13178</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14428</v>
+        <v>14280</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1113</v>
+        <v>-1102</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -838,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12117</v>
+        <v>13875</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12540</v>
+        <v>14280</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-423</v>
+        <v>-405</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -883,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,26 +893,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7280</v>
+        <v>13875</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11765</v>
+        <v>14280</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4485</v>
+        <v>-405</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-332</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13964</v>
+        <v>13875</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11765</v>
+        <v>14280</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2199</v>
+        <v>-405</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -973,7 +973,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -983,26 +983,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nile Air NP-327</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9919</v>
+        <v>9329</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8059</v>
+        <v>12411</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1860</v>
+        <v>-3082</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1028,26 +1028,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9919</v>
+        <v>9329</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8059</v>
+        <v>12411</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1860</v>
+        <v>-3082</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9919</v>
+        <v>9817</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8059</v>
+        <v>7976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1860</v>
+        <v>1841</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1108,7 +1108,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9919</v>
+        <v>9817</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8750</v>
+        <v>7976</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1169</v>
+        <v>1841</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1153,7 +1153,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-410</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>13175</v>
+        <v>9817</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10990</v>
+        <v>7976</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2185</v>
+        <v>1841</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1190,6 +1190,51 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>9817</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>8660</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>1157</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,30 +542,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9956</v>
+        <v>8381</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14280</v>
+        <v>13164</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4324</v>
+        <v>-4783</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -568,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9998</v>
+        <v>10082</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14280</v>
+        <v>13164</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4282</v>
+        <v>-3082</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -601,7 +610,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -613,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10110</v>
+        <v>9050</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14280</v>
+        <v>16106</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4170</v>
+        <v>-7056</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -658,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Air Arabia Egypt E5-321</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10891</v>
+        <v>9136</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14280</v>
+        <v>16106</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3389</v>
+        <v>-6970</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -703,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10891</v>
+        <v>9301</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14280</v>
+        <v>16106</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3389</v>
+        <v>-6805</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -734,9 +743,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -748,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-645</t>
+          <t>Nile Air NP-327</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>13178</v>
+        <v>9301</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14280</v>
+        <v>16106</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1102</v>
+        <v>-6805</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -793,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,30 +812,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-659</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13178</v>
+        <v>9408</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14280</v>
+        <v>16106</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1102</v>
+        <v>-6698</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -838,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,30 +857,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>13875</v>
+        <v>9747</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14280</v>
+        <v>16106</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-405</v>
+        <v>-6359</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -883,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,30 +902,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>13875</v>
+        <v>9747</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14280</v>
+        <v>16106</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-405</v>
+        <v>-6359</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -928,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,17 +947,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>EgyptAir MS-671</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13875</v>
+        <v>10542</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14280</v>
+        <v>16106</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-405</v>
+        <v>-5564</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -959,9 +968,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -983,30 +992,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-327</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9329</v>
+        <v>10556</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12411</v>
+        <v>16106</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3082</v>
+        <v>-5550</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1028,30 +1037,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9329</v>
+        <v>10556</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12411</v>
+        <v>16106</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3082</v>
+        <v>-5550</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1063,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1073,17 +1082,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9817</v>
+        <v>10556</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7976</v>
+        <v>16106</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1841</v>
+        <v>-5550</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1094,9 +1103,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1108,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>flyadeal F3-774</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9817</v>
+        <v>10584</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7976</v>
+        <v>16106</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1841</v>
+        <v>-5522</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1153,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1163,30 +1172,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9817</v>
+        <v>10821</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7976</v>
+        <v>16106</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1841</v>
+        <v>-5285</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1198,43 +1207,2428 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>10821</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-5285</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-308</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>11295</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-4811</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-382</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>11295</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-4811</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-300</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>11295</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-4811</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-330</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>11295</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-4811</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-661</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>11351</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-4755</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-673</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>11435</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-4671</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-663</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>11435</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-4671</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>11435</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-4671</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-388</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>11881</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-4225</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-306</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>11881</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-4225</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-304</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>11881</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-4225</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-574</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>12564</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-3542</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-572</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>12564</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-3542</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-590</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>12564</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-3542</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-659</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>14810</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>16106</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-1296</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-227</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>7126</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-4058</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-127</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>7711</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-3473</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-3026</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-3026</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-3026</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-3026</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-3026</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>8381</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-2803</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-172</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>8381</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-2803</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-663</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>8172</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-3012</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-671</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>9747</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-1437</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>9775</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-1409</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>8172</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>9706</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-1534</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-663</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>8172</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>9706</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-1534</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>8729</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-571</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>8729</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-571</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>8729</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-571</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>8701</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-543</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>8701</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-543</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>8701</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-543</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>8729</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-571</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>8729</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-571</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>8158</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>8729</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-571</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>14-JUN-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>8172</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>8729</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-557</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>29-JUL-26</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-655</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>9817</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>8660</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="D57" s="2" t="n">
+        <v>8813</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>7056</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>1757</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>8813</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>7042</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>1771</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-265</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>11156</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-237</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>03-AUG-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>9706</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>03-AUG-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>9678</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>1241</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>9706</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>9678</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>1241</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-265</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>9678</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>1241</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>9706</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>9678</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>1241</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>11184</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-265</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>10919</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>11156</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-237</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,8 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,19 +465,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,45 +541,1035 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-253</t>
+          <t>SM-451</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-102</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1600</v>
+        <v>9413</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1760</v>
+        <v>13334</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-200</v>
+        <v>-3921</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-127</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>10234</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>13334</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-3100</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>9413</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>12343</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-2930</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>7120</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>16335</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-9215</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>7828</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>16335</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-8507</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-327</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7856</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>16335</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-8479</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>9275</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>16335</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-7060</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-774</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>11027</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>16335</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-5308</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>9852</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-1571</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>9852</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-1571</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>9852</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-1571</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-176</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>6228</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11338</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-5110</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-659</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>11338</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-3057</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-663</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>11338</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-3057</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-673</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>9852</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-1571</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>9852</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-1571</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>9852</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-1571</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>8847</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-566</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>8847</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-566</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>8847</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-566</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>8847</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-566</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>8847</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-566</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>8847</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-566</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
         </is>
       </c>
     </row>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
@@ -56,12 +62,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9413</v>
+        <v>7120</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>13334</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3921</v>
+        <v>-6214</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -596,28 +596,28 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10234</v>
+        <v>8507</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>13334</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3100</v>
+        <v>-4827</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9413</v>
+        <v>9441</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12343</v>
+        <v>13334</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2930</v>
+        <v>-3893</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7120</v>
+        <v>9413</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16335</v>
+        <v>12343</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-9215</v>
+        <v>-2930</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7828</v>
+        <v>9441</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16335</v>
+        <v>12343</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-8507</v>
+        <v>-2902</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-327</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7856</v>
+        <v>8281</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>16335</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-8479</v>
+        <v>-8054</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-321</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9275</v>
+        <v>8281</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>16335</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-7060</v>
+        <v>-8054</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-774</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11027</v>
+        <v>8281</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>16335</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5308</v>
+        <v>-8054</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,28 +911,28 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Air Arabia Egypt E5-321</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8281</v>
+        <v>9279</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9852</v>
+        <v>16335</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1571</v>
+        <v>-7056</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -956,28 +956,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8281</v>
+        <v>6228</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>9852</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1571</v>
+        <v>-3624</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1001,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8281</v>
+        <v>6228</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>9852</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1571</v>
+        <v>-3624</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-176</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6228</v>
+        <v>6384</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11338</v>
+        <v>9852</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-5110</v>
+        <v>-3468</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,507 +1067,12 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>06-JUN-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-659</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>11338</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-3057</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>06-JUN-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-663</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>11338</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-3057</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-673</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>9852</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-1571</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>9852</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-1571</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-665</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>9852</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-1571</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>8847</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-566</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-641</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>8847</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-566</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>8847</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-566</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>8847</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-566</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-641</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>8847</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-566</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-665</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>8847</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-566</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7120</v>
+        <v>7102</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13334</v>
+        <v>13331</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-6214</v>
+        <v>-6229</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8507</v>
+        <v>8497</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13334</v>
+        <v>13331</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4827</v>
+        <v>-4834</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>23</v>
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9441</v>
+        <v>9427</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13334</v>
+        <v>13331</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3893</v>
+        <v>-3904</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9413</v>
+        <v>8511</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12343</v>
+        <v>12331</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2930</v>
+        <v>-3820</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9441</v>
+        <v>9399</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12343</v>
+        <v>12331</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2902</v>
+        <v>-2932</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8281</v>
+        <v>9427</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16335</v>
+        <v>12331</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-8054</v>
+        <v>-2904</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8281</v>
+        <v>8258</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16335</v>
+        <v>16319</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-8054</v>
+        <v>-8061</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8281</v>
+        <v>8258</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16335</v>
+        <v>16319</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-8054</v>
+        <v>-8061</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-321</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9279</v>
+        <v>8258</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>16335</v>
+        <v>16319</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-7056</v>
+        <v>-8061</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Air Arabia Egypt E5-321</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6228</v>
+        <v>13186</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9852</v>
+        <v>16319</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3624</v>
+        <v>-3133</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6228</v>
+        <v>6214</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9852</v>
+        <v>9836</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3624</v>
+        <v>-3622</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6384</v>
+        <v>6214</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9852</v>
+        <v>9836</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3468</v>
+        <v>-3622</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1073,6 +1073,681 @@
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-227</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>6355</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-3481</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-3072</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-3072</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-3072</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-325</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>12738</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1408</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>6214</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-3622</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-172</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>6214</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-3622</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-127</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>6355</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-3481</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-323</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>10288</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +58,6 @@
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -596,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8497</v>
+        <v>7422</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>13331</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4834</v>
+        <v>-5909</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -690,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8511</v>
+        <v>7807</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12331</v>
+        <v>13331</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3820</v>
+        <v>-5524</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -735,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9399</v>
+        <v>8511</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12331</v>
+        <v>13331</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2932</v>
+        <v>-4820</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -776,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9427</v>
+        <v>7807</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>12331</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-2904</v>
+        <v>-4524</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +812,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8258</v>
+        <v>9427</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16319</v>
+        <v>13331</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-8061</v>
+        <v>-3904</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +857,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8258</v>
+        <v>8511</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16319</v>
+        <v>12331</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-8061</v>
+        <v>-3820</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +902,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8258</v>
+        <v>9427</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>16319</v>
+        <v>12331</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-8061</v>
+        <v>-2904</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +947,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-321</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13186</v>
+        <v>6214</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16319</v>
+        <v>9836</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3133</v>
+        <v>-3622</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1001,7 +992,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1046,26 +1037,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>9836</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3622</v>
+        <v>-1578</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1082,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9836</v>
+        <v>11330</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-3481</v>
+        <v>-3072</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1136,7 +1127,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1181,7 +1172,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1217,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11330</v>
+        <v>9836</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3072</v>
+        <v>-3622</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1261,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1262,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-325</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12738</v>
+        <v>6214</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11330</v>
+        <v>9836</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1408</v>
+        <v>-3622</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1316,17 +1307,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6214</v>
+        <v>6355</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>9836</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3622</v>
+        <v>-3481</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1351,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1352,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9836</v>
+        <v>8836</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-3622</v>
+        <v>-578</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1396,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1397,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9836</v>
+        <v>8836</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-3481</v>
+        <v>-578</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1451,7 +1442,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1486,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,7 +1487,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1531,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,7 +1532,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1586,7 +1577,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1621,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8258</v>
+        <v>8906</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8836</v>
+        <v>7130</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-578</v>
+        <v>1776</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1666,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1667,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8258</v>
+        <v>11062</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>8836</v>
+        <v>11330</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-578</v>
+        <v>-268</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1711,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,26 +1712,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-323</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10288</v>
+        <v>11062</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>8836</v>
+        <v>9836</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1452</v>
+        <v>1226</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1748,6 +1739,186 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>11062</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>11062</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-268</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>11062</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>11062</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-268</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -591,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7422</v>
+        <v>7530</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>13331</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5909</v>
+        <v>-5801</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>20</v>
@@ -632,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9427</v>
+        <v>8497</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>13331</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3904</v>
+        <v>-4834</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -684,10 +693,10 @@
         <v>7807</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13331</v>
+        <v>12331</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5524</v>
+        <v>-4524</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -729,10 +738,10 @@
         <v>8511</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13331</v>
+        <v>12331</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4820</v>
+        <v>-3820</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7807</v>
+        <v>8258</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12331</v>
+        <v>16333</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4524</v>
+        <v>-8075</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9427</v>
+        <v>8258</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13331</v>
+        <v>16333</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3904</v>
+        <v>-8075</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8511</v>
+        <v>8258</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12331</v>
+        <v>16333</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3820</v>
+        <v>-8075</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Air Arabia Egypt E5-321</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9427</v>
+        <v>9236</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12331</v>
+        <v>16333</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2904</v>
+        <v>-7097</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7530</v>
+        <v>7526</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>13331</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5801</v>
+        <v>-5805</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>20</v>
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8497</v>
+        <v>9427</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>13331</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4834</v>
+        <v>-3904</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         <v>7807</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12331</v>
+        <v>13331</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4524</v>
+        <v>-5524</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8511</v>
+        <v>8497</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12331</v>
+        <v>13331</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3820</v>
+        <v>-4834</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8258</v>
+        <v>8511</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16333</v>
+        <v>13331</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-8075</v>
+        <v>-4820</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-321</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9236</v>
+        <v>8258</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-7097</v>
+        <v>-8075</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Air Arabia Egypt E5-321</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6214</v>
+        <v>9232</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9836</v>
+        <v>16333</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3622</v>
+        <v>-7101</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>9836</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1578</v>
+        <v>-3622</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>8258</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11330</v>
+        <v>9836</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-3072</v>
+        <v>-1578</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9836</v>
+        <v>11330</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3622</v>
+        <v>-3072</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Air Arabia Egypt E5-325</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6214</v>
+        <v>12736</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9836</v>
+        <v>11330</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-3622</v>
+        <v>1406</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6355</v>
+        <v>6214</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>9836</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3481</v>
+        <v>-3622</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8836</v>
+        <v>9836</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-578</v>
+        <v>-3622</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8258</v>
+        <v>6355</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8836</v>
+        <v>9836</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-578</v>
+        <v>-3481</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8906</v>
+        <v>8258</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>7130</v>
+        <v>8836</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1776</v>
+        <v>-578</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>11062</v>
+        <v>8258</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11330</v>
+        <v>8836</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-268</v>
+        <v>-578</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>11062</v>
+        <v>8906</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9836</v>
+        <v>7130</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1226</v>
+        <v>1776</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1773,10 +1773,10 @@
         <v>11062</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>9836</v>
+        <v>11330</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1226</v>
+        <v>-268</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1818,10 +1818,10 @@
         <v>11062</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11330</v>
+        <v>9836</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-268</v>
+        <v>1226</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1928,6 +1928,96 @@
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>11062</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-451</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>11062</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-268</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,20 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7102</v>
+        <v>6184</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13331</v>
+        <v>9814</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-6229</v>
+        <v>-3630</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7526</v>
+        <v>6184</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13331</v>
+        <v>13319</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5805</v>
+        <v>-7135</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,28 +632,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Air Arabia Egypt E5-321</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9427</v>
+        <v>8739</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13331</v>
+        <v>13319</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3904</v>
+        <v>-4580</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -676,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7807</v>
+        <v>8753</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13331</v>
+        <v>13319</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5524</v>
+        <v>-4566</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8497</v>
+        <v>8753</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13331</v>
+        <v>13319</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4834</v>
+        <v>-4566</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nesma Airlines NE-176</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8511</v>
+        <v>6184</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13331</v>
+        <v>12328</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4820</v>
+        <v>-6144</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -799,7 +790,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +812,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16333</v>
+        <v>12328</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-8075</v>
+        <v>-6144</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +857,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16333</v>
+        <v>12328</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-8075</v>
+        <v>-5990</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +902,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Air Arabia Egypt E5-325</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8258</v>
+        <v>6878</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>16333</v>
+        <v>12328</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-8075</v>
+        <v>-5450</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>30</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,28 +947,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-321</t>
+          <t>Nesma Airlines NE-176</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9232</v>
+        <v>6184</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16333</v>
+        <v>11322</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-7101</v>
+        <v>-5138</v>
       </c>
       <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6214</v>
+        <v>6184</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9836</v>
+        <v>11322</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3622</v>
+        <v>-5138</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,7 +1013,7 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6214</v>
+        <v>6338</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9836</v>
+        <v>11322</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3622</v>
+        <v>-4984</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,7 +1058,7 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,28 +1082,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9836</v>
+        <v>9814</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1578</v>
+        <v>-3630</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,28 +1127,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11330</v>
+        <v>9814</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3072</v>
+        <v>-3630</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1172,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>11330</v>
+        <v>9814</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3072</v>
+        <v>-3476</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,28 +1217,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8258</v>
+        <v>5012</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11330</v>
+        <v>8823</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3072</v>
+        <v>-3811</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1261,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,28 +1262,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-325</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12736</v>
+        <v>5012</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11330</v>
+        <v>8823</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1406</v>
+        <v>-3811</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1306,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,28 +1307,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6214</v>
+        <v>9382</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9836</v>
+        <v>7818</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3622</v>
+        <v>1564</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1351,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,28 +1352,28 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6214</v>
+        <v>9382</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9836</v>
+        <v>7106</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-3622</v>
+        <v>2276</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1396,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,28 +1397,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6355</v>
+        <v>9382</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9836</v>
+        <v>7106</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-3481</v>
+        <v>2276</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1441,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1442,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8258</v>
+        <v>11532</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>8836</v>
+        <v>11322</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-578</v>
+        <v>210</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,7 +1463,7 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1486,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1487,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8258</v>
+        <v>11532</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>8836</v>
+        <v>9814</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-578</v>
+        <v>1718</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,7 +1508,7 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1531,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1545,13 +1536,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8258</v>
+        <v>11532</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8836</v>
+        <v>9814</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-578</v>
+        <v>1718</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1562,7 +1553,7 @@
       <c r="I24" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1576,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1577,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>8258</v>
+        <v>11532</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>8836</v>
+        <v>11322</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-578</v>
+        <v>210</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1607,7 +1598,7 @@
       <c r="I25" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1621,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8258</v>
+        <v>11532</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8836</v>
+        <v>9814</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-578</v>
+        <v>1718</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1652,7 +1643,7 @@
       <c r="I26" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1666,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1680,13 +1671,13 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8258</v>
+        <v>11532</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>8836</v>
+        <v>11322</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-578</v>
+        <v>210</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1697,327 +1688,12 @@
       <c r="I27" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>8906</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>7130</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>1776</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>01-AUG-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>11062</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>11330</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-268</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>03-AUG-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>11062</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>9836</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>05-AUG-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>11062</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>9836</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>08-AUG-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>11062</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>11330</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-268</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>10-AUG-26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>11062</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>9836</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>12-AUG-26</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>11062</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>11330</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>-268</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HBE_JED_threats.xlsx
+++ b/excel_routes/route_HBE_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +533,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6184</v>
+        <v>7286</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9814</v>
+        <v>9729</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3630</v>
+        <v>-2443</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -577,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,30 +578,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-645</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6184</v>
+        <v>7286</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13319</v>
+        <v>9729</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-7135</v>
+        <v>-2443</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,26 +623,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-321</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8739</v>
+        <v>7286</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13319</v>
+        <v>9729</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4580</v>
+        <v>-2443</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -667,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +668,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Air Arabia Egypt E5-325</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8753</v>
+        <v>10841</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13319</v>
+        <v>9729</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4566</v>
+        <v>1112</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8753</v>
+        <v>7286</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13319</v>
+        <v>7741</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4566</v>
+        <v>-455</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -743,9 +734,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +758,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-176</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6184</v>
+        <v>7286</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12328</v>
+        <v>7741</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6144</v>
+        <v>-455</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +803,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6184</v>
+        <v>4954</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12328</v>
+        <v>7741</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6144</v>
+        <v>-2787</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +824,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,30 +848,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6338</v>
+        <v>7286</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12328</v>
+        <v>7741</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5990</v>
+        <v>-455</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,26 +893,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-325</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6878</v>
+        <v>7286</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12328</v>
+        <v>7741</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5450</v>
+        <v>-455</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -937,7 +928,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,17 +938,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-176</t>
+          <t>Nile Air NP-327</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6184</v>
+        <v>4954</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11322</v>
+        <v>7741</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5138</v>
+        <v>-2787</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -982,7 +973,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +983,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6184</v>
+        <v>4954</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11322</v>
+        <v>7741</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5138</v>
+        <v>-2787</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1027,7 +1018,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,26 +1028,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6338</v>
+        <v>7286</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11322</v>
+        <v>7741</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4984</v>
+        <v>-455</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1072,7 +1063,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,17 +1073,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6184</v>
+        <v>4954</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9814</v>
+        <v>7741</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-3630</v>
+        <v>-2787</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1117,7 +1108,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1118,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6184</v>
+        <v>8294</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9814</v>
+        <v>7038</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3630</v>
+        <v>1256</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1153,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,26 +1163,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6338</v>
+        <v>8294</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9814</v>
+        <v>6348</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3476</v>
+        <v>1946</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1198,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,26 +1208,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5012</v>
+        <v>8294</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>8823</v>
+        <v>6348</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3811</v>
+        <v>1946</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1252,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,26 +1253,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5012</v>
+        <v>8294</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8823</v>
+        <v>6348</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-3811</v>
+        <v>1946</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1288,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1311,13 +1302,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9382</v>
+        <v>8294</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7818</v>
+        <v>7038</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1564</v>
+        <v>1256</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1342,7 +1333,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1356,13 +1347,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9382</v>
+        <v>10916</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7106</v>
+        <v>11219</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2276</v>
+        <v>-303</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1387,7 +1378,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1401,13 +1392,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9382</v>
+        <v>10916</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>7106</v>
+        <v>9729</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2276</v>
+        <v>1187</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1432,7 +1423,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1446,13 +1437,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11532</v>
+        <v>10916</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11322</v>
+        <v>9729</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>210</v>
+        <v>1187</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1477,7 +1468,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1491,13 +1482,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11532</v>
+        <v>10916</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9814</v>
+        <v>11219</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1718</v>
+        <v>-303</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1522,7 +1513,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1536,13 +1527,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>11532</v>
+        <v>10916</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9814</v>
+        <v>9729</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1718</v>
+        <v>1187</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1567,7 +1558,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1581,13 +1572,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>11532</v>
+        <v>11868</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11322</v>
+        <v>11219</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>210</v>
+        <v>649</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1604,96 +1595,6 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10-AUG-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>11532</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>9814</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>1718</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>12-AUG-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-451</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>11532</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>11322</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
